--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484734_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484734_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8872</v>
+        <v>9.750500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5616</v>
+        <v>8.192</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3256</v>
+        <v>1.5585</v>
       </c>
       <c r="G2" t="n">
         <v>4.5144</v>
@@ -610,13 +610,13 @@
         <v>3.2079</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1274</v>
+        <v>0.9907</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1997</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9278</v>
+        <v>0.1606</v>
       </c>
       <c r="V2" t="n">
         <v>1.2262</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9158</v>
+        <v>4.8568</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4031</v>
+        <v>5.0796</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4874</v>
+        <v>-0.2228</v>
       </c>
       <c r="G3" t="n">
         <v>3.2785</v>
@@ -688,13 +688,13 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2498</v>
+        <v>0.6913</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2222</v>
+        <v>0.4543</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0276</v>
+        <v>0.237</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6226</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7538</v>
+        <v>1.7724</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3497</v>
+        <v>0.3065</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5958</v>
+        <v>1.4658</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8246</v>
+        <v>0.0438</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6646</v>
+        <v>0.0243</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.16</v>
+        <v>0.0196</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3849</v>
+        <v>0.1468</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0135</v>
+        <v>0.1057</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3984</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2095</v>
+        <v>-0.103</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6511</v>
+        <v>-0.0814</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5584</v>
+        <v>-0.0216</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8991</v>
+        <v>0.5019</v>
       </c>
       <c r="T4" t="n">
-        <v>3.795</v>
+        <v>0.4995</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1041</v>
+        <v>0.0024</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.6606</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3398</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.375</v>
+        <v>0.7446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9886</v>
+        <v>1.1288</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3865</v>
+        <v>-0.3842</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0438</v>
+        <v>-1.8246</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243</v>
+        <v>-1.6646</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0196</v>
+        <v>-0.16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1468</v>
+        <v>0.3849</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1057</v>
+        <v>-1.0135</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>1.3984</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.103</v>
+        <v>-2.2095</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0814</v>
+        <v>-0.6511</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0216</v>
+        <v>-1.5584</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1045</v>
+        <v>1.8899</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1815</v>
+        <v>1.5742</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.077</v>
+        <v>0.3157</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6606</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3398</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>M. LOPEZ VILLENA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4569</v>
+        <v>-0.207</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.264</v>
+        <v>0.2724</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1929</v>
+        <v>-0.4794</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0607</v>
+        <v>-1.6782</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3506</v>
+        <v>-0.7106</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4113</v>
+        <v>-0.9676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0423</v>
+        <v>0.5255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0423</v>
+        <v>-0.1738</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.6992</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.103</v>
+        <v>-2.2036</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3083</v>
+        <v>-0.5369</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4113</v>
+        <v>-1.6668</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3962</v>
+        <v>0.3201</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1176</v>
+        <v>0.2566</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2786</v>
+        <v>0.0635</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9624</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LOPEZ VILLENA</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5606</v>
+        <v>-0.38</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0775</v>
+        <v>-0.1078</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6382</v>
+        <v>-0.2722</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6782</v>
+        <v>-0.0607</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7106</v>
+        <v>0.3506</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9676</v>
+        <v>-0.4113</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5255</v>
+        <v>0.0423</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1738</v>
+        <v>0.0423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6992</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2036</v>
+        <v>-0.103</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5369</v>
+        <v>0.3083</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6668</v>
+        <v>-0.4113</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.1887</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.1322</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3209</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.0335</v>
+        <v>-0.3193</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0617</v>
+        <v>0.0386</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.358</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9624</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1465</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0209</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1256</v>
+        <v>-0.877</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1192</v>
+        <v>-1.4789</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5349</v>
+        <v>-0.4852</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5843</v>
+        <v>-0.9936</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1184</v>
+        <v>-0.6273</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8758</v>
+        <v>0.5399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7574</v>
+        <v>-1.1672</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0008</v>
+        <v>-0.8516</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6591</v>
+        <v>-1.0252</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3417</v>
+        <v>0.1736</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4256</v>
+        <v>-0.5623</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1357</v>
+        <v>0.1049</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2899</v>
+        <v>-0.6672</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.019</v>
+        <v>0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8488</v>
+        <v>1.547</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8678</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1729</v>
+        <v>-1.6921</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.952</v>
+        <v>0.4865</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2209</v>
+        <v>-2.1785</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4789</v>
+        <v>-3.1192</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4852</v>
+        <v>-2.5349</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9936</v>
+        <v>-0.5843</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6273</v>
+        <v>-0.1184</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5399</v>
+        <v>-0.8758</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1672</v>
+        <v>0.7574</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8516</v>
+        <v>-3.0008</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0252</v>
+        <v>-1.6591</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1736</v>
+        <v>-1.3417</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>2.4531</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9393</v>
+        <v>0.88</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9283</v>
+        <v>0.643</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0111</v>
+        <v>0.237</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3018</v>
+        <v>-0.019</v>
       </c>
       <c r="W9" t="n">
-        <v>1.547</v>
+        <v>1.8488</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1154</v>
+        <v>-2.6913</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9044</v>
+        <v>-0.5331</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.211</v>
+        <v>-2.1581</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4117</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5526</v>
+        <v>-0.1285</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.291</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2616</v>
+        <v>-0.2087</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3398</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9547</v>
+        <v>-4.9514</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3777</v>
+        <v>-2.1627</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.577</v>
+        <v>-2.7887</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6627</v>
@@ -1312,13 +1312,13 @@
         <v>2.0757</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0476</v>
+        <v>0.051</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0646</v>
+        <v>0.2796</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.017</v>
+        <v>-0.2286</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5284</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.524800000000002</v>
+        <v>6.406600000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8615</v>
+        <v>12.7433</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.3367</v>
+        <v>-6.336600000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3993</v>
@@ -1390,13 +1390,13 @@
         <v>16.983</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4328</v>
+        <v>4.314800000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8791</v>
+        <v>4.761</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4463000000000002</v>
+        <v>-0.4463</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0004</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.341</v>
+        <v>5.5075</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0793</v>
+        <v>6.5921</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7383</v>
+        <v>-1.0846</v>
       </c>
       <c r="G13" t="n">
         <v>5.7783</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6573</v>
+        <v>-0.1762</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8441</v>
+        <v>0.3569</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1868</v>
+        <v>-0.5331</v>
       </c>
       <c r="V13" t="n">
         <v>0.2828</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2279</v>
+        <v>2.9086</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7282</v>
+        <v>4.118</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5003</v>
+        <v>-1.2093</v>
       </c>
       <c r="G14" t="n">
         <v>2.1051</v>
@@ -1546,13 +1546,13 @@
         <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9528</v>
+        <v>-1.2721</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5168</v>
+        <v>-0.127</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4361</v>
+        <v>-1.1451</v>
       </c>
       <c r="V14" t="n">
         <v>0.9434</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0524</v>
+        <v>1.9188</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0326</v>
+        <v>5.7403</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9803</v>
+        <v>-3.8216</v>
       </c>
       <c r="G15" t="n">
         <v>2.1376</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1417</v>
+        <v>-0.2752</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3121</v>
+        <v>0.0198</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4537</v>
+        <v>-0.295</v>
       </c>
       <c r="V15" t="n">
         <v>1.566</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.877</v>
+        <v>1.1958</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0335</v>
+        <v>0.3258</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8436</v>
+        <v>0.87</v>
       </c>
       <c r="G16" t="n">
         <v>0.4109</v>
@@ -1702,13 +1702,13 @@
         <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0888</v>
+        <v>0.4075</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0123</v>
+        <v>0.3046</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0764</v>
+        <v>0.1029</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.149</v>
+        <v>-0.3453</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7047</v>
+        <v>1.6072</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5557</v>
+        <v>-1.9525</v>
       </c>
       <c r="G19" t="n">
         <v>0.4141</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.02</v>
+        <v>-0.5142</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2787</v>
+        <v>-0.3761</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2587</v>
+        <v>-0.1381</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6226</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8203</v>
+        <v>-1.0374</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2</v>
+        <v>-0.1025</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6204</v>
+        <v>-0.9349</v>
       </c>
       <c r="G20" t="n">
         <v>0.9236</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1022</v>
+        <v>-0.3193</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2199</v>
+        <v>-0.1225</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8823</v>
+        <v>-0.1969</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3208</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0419</v>
+        <v>-1.6532</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6061</v>
+        <v>-0.9241</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4358</v>
+        <v>-0.7291</v>
       </c>
       <c r="G21" t="n">
         <v>0.1539</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1581</v>
+        <v>0.2306</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6808</v>
+        <v>0.0013</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.2294</v>
       </c>
       <c r="V21" t="n">
         <v>0.038</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6184</v>
+        <v>-6.1433</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7111</v>
+        <v>-4.4188</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9074</v>
+        <v>-1.7245</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1556</v>
@@ -2170,13 +2170,13 @@
         <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7835</v>
+        <v>-1.3084</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5879</v>
+        <v>-0.2956</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1956</v>
+        <v>-1.0128</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.3918</v>
+        <v>-7.9271</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1448</v>
+        <v>-7.0217</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.247</v>
+        <v>-0.9054</v>
       </c>
       <c r="G23" t="n">
         <v>-5.016</v>
@@ -2248,13 +2248,13 @@
         <v>0.7548</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9452</v>
+        <v>0.4099</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5618</v>
+        <v>0.6849</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6166</v>
+        <v>-0.2751</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5247</v>
+        <v>-4.8752</v>
       </c>
       <c r="E24" t="n">
-        <v>6.336700000000002</v>
+        <v>6.336700000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.8615</v>
+        <v>-11.2118</v>
       </c>
       <c r="G24" t="n">
         <v>5.399299999999998</v>
@@ -2326,13 +2326,13 @@
         <v>8.4915</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.4329</v>
+        <v>-2.7833</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4461999999999999</v>
+        <v>0.4463</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8792</v>
+        <v>-3.2297</v>
       </c>
       <c r="V24" t="n">
         <v>1.0004</v>
